--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848084</v>
       </c>
       <c r="B2" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128848086</v>
       </c>
       <c r="B3" t="n">
-        <v>95855</v>
+        <v>95861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128848082</v>
       </c>
       <c r="B4" t="n">
-        <v>88750</v>
+        <v>88754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128848086</v>
       </c>
       <c r="B3" t="n">
-        <v>95861</v>
+        <v>95868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128848082</v>
       </c>
       <c r="B4" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848084</v>
       </c>
       <c r="B2" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128848086</v>
       </c>
       <c r="B3" t="n">
-        <v>95868</v>
+        <v>95872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128848082</v>
       </c>
       <c r="B4" t="n">
-        <v>88755</v>
+        <v>88759</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848084</v>
       </c>
       <c r="B2" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128848086</v>
       </c>
       <c r="B3" t="n">
-        <v>95872</v>
+        <v>95879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128848082</v>
       </c>
       <c r="B4" t="n">
-        <v>88759</v>
+        <v>88764</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128848086</v>
       </c>
       <c r="B3" t="n">
-        <v>95887</v>
+        <v>95892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128848082</v>
       </c>
       <c r="B4" t="n">
-        <v>88771</v>
+        <v>88774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848084</v>
       </c>
       <c r="B2" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128848086</v>
       </c>
       <c r="B3" t="n">
-        <v>95892</v>
+        <v>95895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128848082</v>
       </c>
       <c r="B4" t="n">
-        <v>88774</v>
+        <v>88777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848084</v>
       </c>
       <c r="B2" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128848086</v>
       </c>
       <c r="B3" t="n">
-        <v>95895</v>
+        <v>95905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128848082</v>
       </c>
       <c r="B4" t="n">
-        <v>88777</v>
+        <v>88781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848084</v>
       </c>
       <c r="B2" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128848086</v>
       </c>
       <c r="B3" t="n">
-        <v>95905</v>
+        <v>95912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128848082</v>
       </c>
       <c r="B4" t="n">
-        <v>88781</v>
+        <v>88788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848084</v>
       </c>
       <c r="B2" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128848086</v>
       </c>
       <c r="B3" t="n">
-        <v>95912</v>
+        <v>95914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128848082</v>
       </c>
       <c r="B4" t="n">
-        <v>88788</v>
+        <v>88790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128848086</v>
       </c>
       <c r="B3" t="n">
-        <v>95914</v>
+        <v>95940</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128848082</v>
       </c>
       <c r="B4" t="n">
-        <v>88790</v>
+        <v>88791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128848086</v>
       </c>
       <c r="B3" t="n">
-        <v>95940</v>
+        <v>95941</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128848086</v>
       </c>
       <c r="B3" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848084</v>
       </c>
       <c r="B2" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128848086</v>
       </c>
       <c r="B3" t="n">
-        <v>95942</v>
+        <v>95946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128848082</v>
       </c>
       <c r="B4" t="n">
-        <v>88791</v>
+        <v>88794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128848084</v>
+        <v>128848086</v>
       </c>
       <c r="B2" t="n">
-        <v>83011</v>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436826</v>
+        <v>436836</v>
       </c>
       <c r="R2" t="n">
-        <v>7003962</v>
+        <v>7003980</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128848086</v>
+        <v>128848082</v>
       </c>
       <c r="B3" t="n">
-        <v>95946</v>
+        <v>89143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>4405</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436836</v>
+        <v>436791</v>
       </c>
       <c r="R3" t="n">
-        <v>7003980</v>
+        <v>7003938</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128848082</v>
+        <v>128848084</v>
       </c>
       <c r="B4" t="n">
-        <v>88794</v>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4405</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436791</v>
+        <v>436826</v>
       </c>
       <c r="R4" t="n">
-        <v>7003938</v>
+        <v>7003962</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 47988-2025 artfynd.xlsx
+++ b/artfynd/A 47988-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848086</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848082</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848084</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>